--- a/data/WP18/WP18_sachgebiete_FDP_zeitreihe.xlsx
+++ b/data/WP18/WP18_sachgebiete_FDP_zeitreihe.xlsx
@@ -1811,13 +1811,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEA0D475-8B82-4FA4-98DB-126E84C72CD4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7428AC75-30F9-44C7-B4A0-0DD9720C4FEF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCDF7D0F-D061-4655-B435-E296B1CA6C13}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEDDA7B5-FFC8-4C75-BA7F-0DF74328A4E9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09AEECA1-71F8-41EF-B084-6149C250D1DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B71C65CE-139C-4B4C-9535-C19554B1C433}"/>
 </file>
--- a/data/WP18/WP18_sachgebiete_FDP_zeitreihe.xlsx
+++ b/data/WP18/WP18_sachgebiete_FDP_zeitreihe.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t xml:space="preserve">periode</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t xml:space="preserve">Bauwesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wohnungswesen</t>
   </si>
   <si>
     <t xml:space="preserve">Glücksspiel</t>
@@ -803,7 +806,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="s">
         <v>8</v>
@@ -835,7 +838,7 @@
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G15" t="n">
         <v>4</v>
@@ -846,7 +849,7 @@
         <v>45139</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" t="n">
         <v>5</v>
@@ -858,7 +861,7 @@
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
         <v>4</v>
@@ -869,7 +872,7 @@
         <v>45170</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" t="n">
         <v>52</v>
@@ -881,7 +884,7 @@
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G17" t="n">
         <v>3</v>
@@ -898,7 +901,7 @@
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
@@ -921,7 +924,7 @@
         <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" t="n">
         <v>33</v>
@@ -944,7 +947,7 @@
         <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" t="n">
         <v>34</v>
@@ -967,7 +970,7 @@
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
@@ -984,19 +987,19 @@
         <v>45323</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C22" t="n">
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -1007,7 +1010,7 @@
         <v>45352</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C23" t="n">
         <v>5</v>
@@ -1019,7 +1022,7 @@
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G23" t="n">
         <v>3</v>
@@ -1030,13 +1033,13 @@
         <v>45383</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -1059,7 +1062,7 @@
         <v>3</v>
       </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
@@ -1082,7 +1085,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
@@ -1105,7 +1108,7 @@
         <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E27" t="n">
         <v>9</v>
@@ -1122,7 +1125,7 @@
         <v>45505</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28" t="n">
         <v>8</v>
@@ -1134,7 +1137,7 @@
         <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G28" t="n">
         <v>5</v>
@@ -1151,7 +1154,7 @@
         <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E29" t="n">
         <v>6</v>
@@ -1168,13 +1171,13 @@
         <v>45566</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C30" t="n">
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E30" t="n">
         <v>4</v>
@@ -1191,13 +1194,13 @@
         <v>45597</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31" t="n">
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -1249,7 +1252,7 @@
         <v>3</v>
       </c>
       <c r="F33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G33" t="n">
         <v>3</v>
@@ -1266,13 +1269,13 @@
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E34" t="n">
         <v>4</v>
       </c>
       <c r="F34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G34" t="n">
         <v>3</v>
@@ -1283,7 +1286,7 @@
         <v>45717</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C35" t="n">
         <v>6</v>
@@ -1318,7 +1321,7 @@
         <v>5</v>
       </c>
       <c r="F36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G36" t="n">
         <v>4</v>
@@ -1329,10 +1332,10 @@
         <v>45778</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C37" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -1341,7 +1344,7 @@
         <v>5</v>
       </c>
       <c r="F37" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G37" t="n">
         <v>4</v>
@@ -1352,19 +1355,19 @@
         <v>45809</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C38" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E38" t="n">
         <v>4</v>
       </c>
       <c r="F38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G38" t="n">
         <v>4</v>
@@ -1410,7 +1413,7 @@
         <v>21</v>
       </c>
       <c r="F40" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G40" t="n">
         <v>3</v>
@@ -1444,19 +1447,19 @@
         <v>45931</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C42" t="n">
         <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E42" t="n">
         <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G42" t="n">
         <v>2</v>
@@ -1473,13 +1476,13 @@
         <v>54</v>
       </c>
       <c r="D43" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E43" t="n">
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G43" t="n">
         <v>2</v>
@@ -1536,19 +1539,19 @@
         <v>46054</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C46" t="n">
         <v>16</v>
       </c>
       <c r="D46" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E46" t="n">
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G46" t="n">
         <v>5</v>
@@ -1559,7 +1562,7 @@
         <v>46082</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C47" t="n">
         <v>10</v>
@@ -1571,7 +1574,7 @@
         <v>5</v>
       </c>
       <c r="F47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G47" t="n">
         <v>5</v>
@@ -1811,13 +1814,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7428AC75-30F9-44C7-B4A0-0DD9720C4FEF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63945846-BC33-47D2-836D-EFCCDADF8808}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEDDA7B5-FFC8-4C75-BA7F-0DF74328A4E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDF28A7C-68EF-43B8-A8DF-F9F2CB4EAFF6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B71C65CE-139C-4B4C-9535-C19554B1C433}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8705CBB-E730-4CB6-A7EA-56F403EEAF78}"/>
 </file>
--- a/data/WP18/WP18_sachgebiete_FDP_zeitreihe.xlsx
+++ b/data/WP18/WP18_sachgebiete_FDP_zeitreihe.xlsx
@@ -1814,13 +1814,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63945846-BC33-47D2-836D-EFCCDADF8808}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA6624A9-88C8-4F4C-ADAA-198856AFA18A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDF28A7C-68EF-43B8-A8DF-F9F2CB4EAFF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B02B74C0-A7EB-40E1-A011-C56F5A4A2B75}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8705CBB-E730-4CB6-A7EA-56F403EEAF78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C79B905-4FED-4B5F-9254-580C6848A8CE}"/>
 </file>